--- a/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
+++ b/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="104">
   <si>
     <t>参数项</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -54,721 +54,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不加条件查询</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">createCL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.createCL(&lt; name &gt;,[ options ])</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:Compressed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:IsMainCL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:AutoSplit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:Group</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:AutoIndexId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">IsMainCL:true|false
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Compressed:true|false</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、取值非法，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>test
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、空串</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AutoSplit:true|false
-AutoSplit 必须配合散列分区和域使用，且不能与 Group 同时使用。
-如果在集合中没有指定AutoSplit，则使用所属域中的AutoSplit参数。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Group必须存在于集合空间所属的域中（所有复制组均属于SYSDOMAIN，即如果集合空间没有指定域，则系统内任意复制组均可）。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、不指定Compressed，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、Compressed:true|false</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、不指定IsMainCL，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、IsMainCL:true|false</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、ShardingType:"hash"，AutoSplit:true，且不指定Group
-2、AutoSplit:false
-3、域中AutoSplit:true，CL不指定AutoSplit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、取值非法，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>test
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、空串</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ShardingType:"range"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AutoSplit:true
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AutoSplit:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Group</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一起使用，如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AutoSplit:false,Group:group1
-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、取值非法，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>test
-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、空串</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、所属CS指定域，指定CL的Group为CS所属域中的group
-2、所属CS不指定域，指定CL的Group为系统内任意复制组</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、所属CS指定域，指定CL的Group为CS所属域中的group
-2、空串
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AutoIndexId:true|false</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、不指定Compressed，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、Compressed:true|false</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CL必须存在</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">dropCL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.dropCL(&lt; name &gt;)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">getCL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.getCL(&lt; name &gt;)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>已存在的CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，非系统CS</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、不存在的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>系统</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、空串，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.dropCL(“”)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、不指定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.dropCL()</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>已存在的CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、不存在的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、空串，如db.collectionspace.getCL(“”)
-4、不指定CL，如db.collectionspace.getCL()</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">listCollections
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.listCollections()</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、加条件查询，如：db.listCollections(“test”)
-2、空串，如：db.listCollections(‘’)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>子特性</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -778,10 +67,6 @@
   </si>
   <si>
     <t>lob</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>subCL</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2658,6 +1943,36 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>file path</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要拥有文件的读权限。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、文件路径正确，且有文件权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、文件路径错误
+2、当前用户没有操作文件的权限
+3、空串，如：db.foo.bar.putLob('')</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">putLob
 </t>
@@ -2672,6 +1987,15 @@
       </rPr>
       <t>语法：</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.putLob(&lt;file path&gt;)</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2689,6 +2013,15 @@
       </rPr>
       <t>语法：</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.deleteLob(&lt;oid&gt;)</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2706,6 +2039,186 @@
       </rPr>
       <t>语法：</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.getLob(&lt;oid&gt;,&lt;file path&gt;,[forced])</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>oid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除存在的OID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不存在
+2、空串，如：db.collectionspace.collection.deleteLob()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>forced</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string，本地文件不需要事先手工创建。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>存在</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不存在
+2、空串，如：db.collectionspace.collection.getLob('','/opt/newlob')</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、路径存在，文件存在
+2、路径不存在</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">bool:true|false
+forced 默认为 false。
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、无效取值，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>forced:test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、空串，如orced:</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2723,18 +2236,19 @@
       </rPr>
       <t>语法：</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>file path</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要拥有文件的读权限。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、文件路径正确，且有文件权限</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.listLobs()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不指定查询条件：db.collectionspace.collection.listLobs()</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2749,10 +2263,130 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、
-2、
-3、</t>
-    </r>
+      <t>、路径没有可写权限，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>file path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/home/test/newlob</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，但是当前用户没有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/home/test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的操作权限
+2、空串，如：db.foo.bar.getLob('5435e7b69487faa663000897','')</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>指定查询条件，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.listLobs('5435e7b69487faa663000897)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>subCL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">attachCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.attachCL(&lt;subCLFullName&gt;, &lt;options&gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>subCLFullName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:两个字段“LowBound”（区间左值）以及“UpBound”（区间右值）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在的集合</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2767,9 +2401,117 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、文件路径错误
-2、当前用户没有操作文件的权限
-3、空串，如：db.foo.bar.putLob('/opt/mylob')</t>
+      <t>、不指定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>forced</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取默认值
+2、bool:true|false</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、主子表属于同一个CS
+2、主子表属于不同CS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、集合不存在
+2、空串，如：db.foo.year.attachCL("",{LowBound:{date:"20130101"},UpBound:{date:"20130131"}})</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效区间：
+[-inf，n)
+[n,m)    --（n&lt;m）
+[m,inf)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无效区间：
+[n,m)  ---n&gt;m
+[n,n)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">detachCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.detachCL(&lt;subCLFullName&gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>左开右闭</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string，集合存在</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合存在</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、集合不存在
+2、空串，如db.collectionspace.collection.detachC()</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2972,7 +2714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2982,9 +2724,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3016,7 +2755,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3028,12 +2794,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3041,27 +2801,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3358,686 +3097,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="26.125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="31.875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="26.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="26.125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="31.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="26.5" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1">
-      <c r="A1" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="19" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="7" customFormat="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+    <row r="2" spans="1:8" s="6" customFormat="1">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="114.75">
-      <c r="A3" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>50</v>
+      <c r="A3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="296.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="27"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>55</v>
+        <v>27</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="76.5">
-      <c r="A5" s="25"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="27"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="25"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="27"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" ht="153">
-      <c r="A7" s="25"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="27"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" ht="153">
-      <c r="A8" s="25"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>55</v>
+        <v>34</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" ht="102">
-      <c r="A9" s="25"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="27"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>55</v>
+        <v>37</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="127.5">
-      <c r="A10" s="25"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="27"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" ht="140.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>55</v>
+        <v>39</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" ht="140.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="127.5">
-      <c r="A13" s="25"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="28"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="14" t="s">
+      <c r="A14" s="22"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>54</v>
+      <c r="H14" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="102">
-      <c r="A15" s="25"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" ht="153">
-      <c r="A16" s="25"/>
-      <c r="B16" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>48</v>
+      <c r="A16" s="22"/>
+      <c r="B16" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>91</v>
+        <v>65</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="102">
-      <c r="A17" s="25"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="14" t="s">
-        <v>49</v>
+      <c r="A17" s="22"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="25"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="14" t="s">
-        <v>88</v>
+      <c r="A18" s="22"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="25.5">
-      <c r="A19" s="29"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="30" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="53.25">
+      <c r="A20" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="53.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="53.25" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="78.75">
+      <c r="A23" s="17"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="38.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="53.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="64.5">
+      <c r="A26" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="1" t="s">
+      <c r="B26" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" ht="63.75">
+      <c r="A27" s="17"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="5"/>
     </row>
-    <row r="20" spans="1:8" ht="51.75">
-      <c r="A20" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="13" t="s">
+    <row r="28" spans="1:8" ht="53.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C28" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" ht="39">
-      <c r="A21" s="15"/>
-      <c r="B21" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" ht="39">
-      <c r="A22" s="15"/>
-      <c r="B22" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" ht="39">
-      <c r="A23" s="15"/>
-      <c r="B23" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="15"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="15"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="15"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8" ht="38.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" ht="38.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="1:8" ht="67.5">
-      <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:8" ht="51">
-      <c r="A32" s="15"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:8" ht="27">
-      <c r="A33" s="15"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="1:8" ht="67.5">
-      <c r="A34" s="15"/>
-      <c r="B34" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="1:8" ht="64.5">
-      <c r="A35" s="15"/>
-      <c r="B35" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="1:8" ht="51">
-      <c r="A36" s="15"/>
-      <c r="B36" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H36" s="6"/>
+      <c r="H28" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A3:A19"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="A24:A36"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B3:B15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
+++ b/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
@@ -250,638 +250,6 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、字段值无效取值（覆盖无效边界）：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-int</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-214748364</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>214748364</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-922337203685477580</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>922337203685477580</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-float</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>E-308</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>E+308
-string:16.5M
-oid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">位字节
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>bool</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>test
-date:1902-01-17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2038-01-19
-timestamp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1902-01-17-00.00.00.000000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">2038-01-19-00.00.00.000000
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>binary(Base64)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>regex</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>subobj</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>array(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数组</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>null</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>minkey</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>maxkey</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、更新的字段值跟原字段值数据类型不一致，如插入的是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>int</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">数组，更新的字段值为字符串
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>空串，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">{$inc:{a:}}    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    {$inc:}</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>、字段值无效取值</t>
     </r>
     <r>
@@ -1700,11 +1068,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Json 对象，格式：{""更新符1"":{字段名1:"值"},"更新符2":{"字段名2":"值2"},...}
-update 本版本暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，将自动剔除掉对分区键的更新，但其他字段更新生效，且不会发生错误。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -2512,6 +1875,635 @@
       </rPr>
       <t>、集合不存在
 2、空串，如db.collectionspace.collection.detachC()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Json 对象，格式：{""更新符1"":{字段名1:"值"},"更新符2":{"字段名2":"值2"},...}
+update 本版本暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，将自动剔除掉对分区键的更新，但其他字段更新生效，且不会发生错误。
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、字段值无效取值（覆盖无效边界）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-214748364</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>214748364</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+long</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-922337203685477580</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>922337203685477580</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>E-308</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>E+308
+string:16.5M
+oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">位字节
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>bool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test
+date:1902-01-17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2038-01-19
+timestamp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1902-01-17-00.00.00.000000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">2038-01-19-00.00.00.000000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>binary(Base64)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>regex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>subobj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>array(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数组</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>minkey</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>maxkey</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、更新的字段值跟原字段值数据类型不一致，如插入的是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">数组，更新的字段值为字符串
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">{$inc:{a:}}    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    {$inc:}
+</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2714,7 +2706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2758,14 +2750,35 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2784,24 +2797,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3112,55 +3107,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
-    <row r="3" spans="1:8" ht="114.75">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:8" ht="127.5">
+      <c r="A3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="25" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>4</v>
@@ -3168,15 +3163,15 @@
       <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>64</v>
+      <c r="G3" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="296.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="19"/>
+    <row r="4" spans="1:8" ht="323.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="1" t="s">
         <v>27</v>
       </c>
@@ -3186,15 +3181,15 @@
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>29</v>
+      <c r="G4" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="76.5">
-      <c r="A5" s="22"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
@@ -3205,14 +3200,14 @@
         <v>24</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="22"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
@@ -3220,142 +3215,142 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" ht="153">
-      <c r="A7" s="22"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" ht="153">
-      <c r="A8" s="22"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" ht="102">
-      <c r="A9" s="22"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="127.5">
-      <c r="A10" s="22"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" ht="140.25">
-      <c r="A11" s="22"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" ht="140.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="127.5">
-      <c r="A13" s="22"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="20"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="11" t="s">
         <v>18</v>
       </c>
@@ -3366,102 +3361,102 @@
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="102">
-      <c r="A15" s="22"/>
-      <c r="B15" s="29"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" ht="153">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24" t="s">
-        <v>54</v>
+      <c r="A16" s="29"/>
+      <c r="B16" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="102">
-      <c r="A17" s="22"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="22"/>
-      <c r="B18" s="25"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="25.5">
-      <c r="A19" s="23"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="8" t="s">
@@ -3470,210 +3465,203 @@
       <c r="F19" s="1"/>
       <c r="G19" s="11"/>
       <c r="H19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="53.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="G20" s="13" t="s">
         <v>67</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="53.25">
-      <c r="A21" s="17"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="53.25" customHeight="1">
-      <c r="A22" s="17"/>
-      <c r="B22" s="24" t="s">
-        <v>72</v>
+      <c r="A22" s="16"/>
+      <c r="B22" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="78.75">
-      <c r="A23" s="17"/>
-      <c r="B23" s="25"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="38.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="26"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="53.25">
-      <c r="A25" s="17"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="8"/>
       <c r="F25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="64.5">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="63.75">
-      <c r="A27" s="17"/>
-      <c r="B27" s="25"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="53.25">
-      <c r="A28" s="17"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H28" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="B22:B24"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -3682,6 +3670,13 @@
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A3:A19"/>
     <mergeCell ref="B16:B19"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="B22:B24"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
+++ b/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
@@ -15,8 +15,70 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不同数据类型处理逻辑是否一样？如果一样可以不用覆盖所有类型</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+放插入里面测试</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="106">
   <si>
     <t>参数项</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -67,10 +129,6 @@
   </si>
   <si>
     <t>lob</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据修改操作</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -109,6 +167,580 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">cond
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">hint
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>匹配符在余婷的设计里面覆盖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、记录中数组字段名存在，指定的值也存在
+2、记录中数组字段名存在，指定的值不存在
+3、记录中数组字段名不存在
+4、字段值有效取值  ---同$inc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、指定的字段名在记录中已存在，非数组
+2、空串，如：{$pull:{&lt;字段名1&gt;:}}  或  {$pull:{"":""}}
+3、字段值无效取值   ---同$inc</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、指定的字段名在记录中已存在，非数组
+2、空串，如：{$pull_all:{&lt;字段名1&gt;:[,,]  或  {$pull_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
+3、字段值无效取值   ---同$inc</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、指定的字段名在记录中已存在，非数组
+2、空串，如：{$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
+3、字段值无效取值   ---同$inc</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、指定的字段名在记录中已存在，非数组
+2、空串，如：{$push_all:{&lt;字段名1&gt;:[,,]  或  {$push_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
+3、字段值无效取值   ---同$inc</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、记录中数组字段名存在，指定的值也存在
+2、记录中数组字段名存在，指定的值不存在
+3、记录中数组字段名不存在
+4、指定清除一个字段名里面的多个值
+5、字段值有效取值  ---同$inc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段名存在
+2、字段名不存在
+3、字段值有效取值  ---同$inc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段名为空串
+2、格式错误</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段值为null，如：{"":null}
+2、字段值不为空，如：{"":"&lt; indexname &gt;"}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>setOnInsert</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在做插入操作时向插入的记录中设置字段。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、文件路径错误
+2、当前用户没有操作文件的权限
+3、空串，如：db.foo.bar.putLob('')</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">putLob
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.putLob(&lt;file path&gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">deleteLob
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.deleteLob(&lt;oid&gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">getLob
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.getLob(&lt;oid&gt;,&lt;file path&gt;,[forced])</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>oid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不存在
+2、空串，如：db.collectionspace.collection.deleteLob()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>存在</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>oid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不存在
+2、空串，如：db.collectionspace.collection.getLob('','/opt/newlob')</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、无效取值，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>forced:test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、空串，如orced:</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">listLobs
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.listLobs()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不指定查询条件：db.collectionspace.collection.listLobs()</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>指定查询条件，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.listLobs('5435e7b69487faa663000897)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>subCL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">attachCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.attachCL(&lt;subCLFullName&gt;, &lt;options&gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>subCLFullName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在的集合</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不指定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>forced</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，取默认值
+2、bool:true|false</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、集合不存在
+2、空串，如：db.foo.year.attachCL("",{LowBound:{date:"20130101"},UpBound:{date:"20130131"}})</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">detachCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.collection.detachCL(&lt;subCLFullName&gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string，集合存在</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">rule
 </t>
     </r>
@@ -122,78 +754,6 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">cond
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">hint
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、为空时，更新所有记录，不为空时，更新符合条件的记录。
-2、格式：[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}]  
-匹配符：$gt、$gte、$lt、$lte……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>匹配符在余婷的设计里面覆盖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、更新1个字段的值,如：{""更新符1"":{字段名1:"值"}}
-2、更新多个字段的值，如：{"更新符2":{"字段名2":"值2"，"字段名3":"值3"}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$unset，删除集合中指定的字段名。如果记录中没有指定的字段名，跳过。
-语法：{$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$set，将指定的“&lt;字段名&gt;”更新为指定的“&lt;值&gt;”，如果字段名不存在则补充，如果存在则更新
-语法：{$set:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$inc，给指定“&lt;字段名&gt;”增加指定的“&lt;值&gt;”，如果字段名不存在则补充，如果存在则更新
-语法：{$inc:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -239,139 +799,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、字段值无效取值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  ---</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">同上
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、更新的字段值与原字段值数据类型不一致</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">、空串
-</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、空串，如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>{$unset:{"":""}</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>1、字段名存在
 2、字段名不存在</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>更新符：$addtose，向数组对象中添加元素和值，操作对象必须为数组类型的字段；
-如果字段名存在值也存在，则跳过不添加；如果字段名存在值不存在，则只添加值。
-如果字段名不存在则添加字段名和值。
-语法：{$addtoset:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]，&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$pop，删除指定数组对象（&lt;字段名1&gt;,&lt;字段名2&gt;,...）最后 N 个元素，操作对象必须为数组类型的字段。如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的 N 值大于数组对象的长度，数组对象的长度更新为0，即它的元素全部被删除；如果指定的 N 值 &lt; 0，意味着从数组起始删除第 -N 个元素。
-语法：{$pop:{&lt;字段名1&gt;:,&lt;字段名2&gt;:,...}}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、字段名取值为：-1、0、-1
-2、字段名取值等于数组字段值个数，如age:[1,1,1,1]，指定pop字段值为4|-4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1</t>
     </r>
@@ -383,64 +815,6 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、字段名取值大于数组字段值个数，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>age:[1,1,1,1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，指定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>pop</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字段值为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>5|-5
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>、空串，如：</t>
     </r>
     <r>
@@ -450,173 +824,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>{$pop:{&lt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字段名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">1&gt;:}}   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  {$pop:{"":}}
-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、取值非整数，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>{$pop:{age:test}}</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>更新符：$pull，清除指定数组对象的指定值。操作对象必须为数组类型的字段。如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
-语法：{$pull:{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;字段名1&gt;:&lt;值1&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>更新符：$pull_all，清除指定数组对象的指定值。操作对象必须为数组类型的字段。如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
-语法：{$pull_all:{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>更新符：$push，将给定数值插入到目标数组中，操作对象必须为数组类型的字段。如果记录中不存在指定的字段名，将指定的字段名以数组对象的形式推入到记录中并填充其指定的数值；如果记录中存在指定的字段名，且字段名存在指定的数值，指定的数值也会被推入到记录中。
-语法：{$push:{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;字段名1&gt;:&lt;值1&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。如果记录中不存在指定的数组对象，向记录推入指定的数组对象和每一个指定的值；如果指定的值存在数组对象中，同样被推入到数组对象中。
-语法：{$push_all:{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+      <t>{$unset:{"":""}</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -646,6 +854,14 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>1、文件路径正确，且有文件权限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string，本地文件不需要事先手工创建。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>1</t>
     </r>
@@ -657,9 +873,8 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、指定的字段名在记录中已存在，非数组
-2、空串，如：{$pull:{&lt;字段名1&gt;:}}  或  {$pull:{"":""}}
-3、字段值无效取值   ---同$inc</t>
+      <t>、路径存在，文件不存在
+2、路径不存在</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -675,10 +890,86 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、指定的字段名在记录中已存在，非数组
-2、空串，如：{$pull_all:{&lt;字段名1&gt;:[,,]  或  {$pull_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
-3、字段值无效取值   ---同$inc</t>
-    </r>
+      <t>、路径没有可写权限，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>file path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/home/test/newlob</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，但是当前用户没有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/home/test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的操作权限
+2、空串，如：db.foo.bar.getLob('5435e7b69487faa663000897','')
+3、文件已存在</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>forced</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、主子表属于同一个CS
+2、主子表属于不同CS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无效区间：
+[n,m)  ---n&gt;m
+[n,n)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合存在</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -693,10 +984,14 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、指定的字段名在记录中已存在，非数组
-2、空串，如：{$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
-3、字段值无效取值   ---同$inc</t>
-    </r>
+      <t>、集合不存在
+2、空串，如db.collectionspace.collection.detachC()
+3、直接写子表名称，不标注CS</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据修改操作</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -711,24 +1006,151 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、指定的字段名在记录中已存在，非数组
-2、空串，如：{$push_all:{&lt;字段名1&gt;:[,,]  或  {$push_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
-3、字段值无效取值   ---同$inc</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、记录中数组字段名存在，指定的值也存在
-2、记录中数组字段名存在，指定的值不存在
-3、记录中数组字段名不存在
-4、指定清除一个字段名里面的多个值
-5、字段值有效取值  ---同$inc</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、字段名存在
-2、字段名不存在
-3、字段值有效取值  ---同$inc</t>
+      <t>、字段值无效取值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  ---</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">同上
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">、更新的字段值与原字段值数据类型不一致
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">、空串
+</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>{$pop:{&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1&gt;:}}   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  {$pop:{"":}}
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、取值非整数，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>{$pop:{age:test}}</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -854,7 +1276,7 @@
         <family val="1"/>
       </rPr>
       <t>2&gt;,...}}
-3</t>
+2</t>
     </r>
     <r>
       <rPr>
@@ -897,17 +1319,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1、字段名为空串
-2、格式错误</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、字段值为null，如：{"":null}
-2、字段值不为空，如：{"":"&lt; indexname &gt;"}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、格式错误</t>
+    <t>1、为空时，更新所有记录，不为空时，更新符合条件的记录。
+2、格式：[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}]  
+匹配符：$gt、$gte、$lt、$lte……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段名存在，为空
+2、按匹配符匹配记录更新</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、hint 参数是一个包含一个单一字段的 Json 对象，字段名会被忽略，而其字段值则指定为需要访问索引的名称，当字段值为 null 时，则遍历集合中所有的记录，它的格式为{"":null}或者{"":"&lt; indexname &gt;"}
+2、格式：[{"":"索引名"|null}]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式错误</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -929,6 +1357,63 @@
       <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> cond </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参数在集合中匹配不到记录时，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">update </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不做任何操作，而</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.249977111117893"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -937,88 +1422,22 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>方法跟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> update </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>方法都是对记录进行更新，不同的是当使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> cond </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>参数在集合中匹配不到记录时，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">update </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不做任何操作，而</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> upsert </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>方法会做一次插入操作。
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方法会做一次插入操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。
 语法：</t>
     </r>
     <r>
@@ -1030,31 +1449,6 @@
       </rPr>
       <t>db.collectionspace.collection.upsert(&lt;rule&gt;,[cond],[hint],[setOnInsert])</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>setOnInsert</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>同update</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>在做插入操作时向插入的记录中设置字段。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、hint 参数是一个包含一个单一字段的 Json 对象，字段名会被忽略，而其字段值则指定为需要访问索引的名称，当字段值为 null 时，则遍历集合中所有的记录，它的格式为{"":null}或者{"":"&lt; indexname &gt;"}
-2、格式：[{"":"索引名"|null}]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1063,246 +1457,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1、字段名存在，为空
-2、按匹配附匹配记录更新</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、字段名不存在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、更新符错误，如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>{"test":{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字段名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1:"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"}}
-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、空串，如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>{"":{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字段名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1:"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">"}}  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">  {"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字段名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1":{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>字段名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1:""}}
-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">、格式错误
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、指定更新的字段名为分区键</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Json 对象，格式：{&lt;{""更新符1"":{"字段名1":"值"},"更新符2":{"字段名2":"值2"},...}&gt;,[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}],[{"":"索引名"|null}]}
-upsert 本版本暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，将自动剔除掉对分区键的更新，但其他字段更新生效，且不会发生错误。</t>
+    <t>需要拥有文件的读权限。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除存在的OID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1310,504 +1469,8 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>需要拥有文件的读权限。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、文件路径正确，且有文件权限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、文件路径错误
-2、当前用户没有操作文件的权限
-3、空串，如：db.foo.bar.putLob('')</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">putLob
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.putLob(&lt;file path&gt;)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">deleteLob
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.deleteLob(&lt;oid&gt;)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">getLob
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.getLob(&lt;oid&gt;,&lt;file path&gt;,[forced])</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>oid</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除存在的OID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>oid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不存在
-2、空串，如：db.collectionspace.collection.deleteLob()</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>forced</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string，本地文件不需要事先手工创建。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>oid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>存在</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>oid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不存在
-2、空串，如：db.collectionspace.collection.getLob('','/opt/newlob')</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、路径存在，文件存在
-2、路径不存在</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">bool:true|false
-forced 默认为 false。
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、无效取值，如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>forced:test</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、空串，如orced:</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">listLobs
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.listLobs()</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不指定查询条件：db.collectionspace.collection.listLobs()</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、路径没有可写权限，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>file path</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>/home/test/newlob</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，但是当前用户没有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>/home/test</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>的操作权限
-2、空串，如：db.foo.bar.getLob('5435e7b69487faa663000897','')</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>指定查询条件，如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.listLobs('5435e7b69487faa663000897)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>subCL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">attachCL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.attachCL(&lt;subCLFullName&gt;, &lt;options&gt;)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>subCLFullName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:两个字段“LowBound”（区间左值）以及“UpBound”（区间右值）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已存在的集合</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、不指定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>forced</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，取默认值
-2、bool:true|false</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、主子表属于同一个CS
-2、主子表属于不同CS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、集合不存在
-2、空串，如：db.foo.year.attachCL("",{LowBound:{date:"20130101"},UpBound:{date:"20130131"}})</t>
-    </r>
+    <t>bool:true|false
+forced 默认为 false。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1818,70 +1481,284 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>无效区间：
-[n,m)  ---n&gt;m
-[n,n)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">detachCL
+    <t>options:LowBound/UpBound</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>“LowBound”（区间左值）以及“UpBound”（区间右值）
+左开右闭</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、更新1个字段的值,如：{""更新符1"":{字段名1:"值"}}
+2、更新多个字段的值，如：{"更新符2":{"字段名2":"值2"，"字段名3":"值3"}}
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>db.collectionspace.collection.detachCL(&lt;subCLFullName&gt;)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>左开右闭</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string，集合存在</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合存在</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、部分字段为分区键字段（覆盖所有的更新符）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+4、全部字段为分区键字段</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>1</t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、集合不存在
-2、空串，如db.collectionspace.collection.detachC()</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Json 对象，格式：{""更新符1"":{字段名1:"值"},"更新符2":{"字段名2":"值2"},...}
-update 本版本暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，将自动剔除掉对分区键的更新，但其他字段更新生效，且不会发生错误。
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、字段名不存在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、更新符错误，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>{"test":{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1:"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"}}
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>{"":{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1:"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"}}  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  {"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1":{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1:""}}
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">、格式错误
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唯一索引，修改唯一索引的值重复</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1896,7 +1773,45 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>、字段值无效取值（覆盖无效边界）：</t>
+      <t>、字段值无效取值（覆盖无效边界）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原始值为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
     </r>
     <r>
       <rPr>
@@ -2375,6 +2290,37 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>minkey</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">：
 </t>
     </r>
@@ -2385,26 +2331,6 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>minkey</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>maxkey</t>
     </r>
     <r>
@@ -2502,9 +2428,194 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">    {$inc:}
-</t>
-    </r>
+      <t xml:space="preserve">    {$inc:}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$inc，给指定“&lt;字段名&gt;”增加指定的“&lt;值&gt;”
+如果字段名不存在则补充，如果存在则更新。
+语法：{$inc:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$set，将指定的“&lt;字段名&gt;”更新为指定的“&lt;值&gt;”
+如果字段名不存在则补充，如果存在则更新。
+语法：{$set:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$unset，删除集合中指定的字段名。
+如果记录中没有指定的字段名，跳过。
+语法：{$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$addtose，向数组对象中添加元素和值，操作对象必须为数组类型的字段；
+如字段名存在值也存在，则跳过不添加；如果字段名存在值不存在，则只添加值；如果字段名不存在则添加字段名和值。
+语法：{$addtoset:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]，&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$pop，删除指定数组对象最后 N 个元素，操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的 N 值大于数组对象的长度，数组对象的长度更新为0，即它的元素全部被删除；如果指定的 N 值 &lt; 0，即从数组起始删除第 -N 个元素。
+语法：{$pop:{&lt;字段名1&gt;:,&lt;字段名2&gt;:,...}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、有效取值为：-1、0、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、取值等于数组字段值个数，如age:[1,1,1,1]，指定pop字段值为4|-4
+3、取值大于数组字段值个数，如age:[1,1,1,1]，指定pop字段值为5|-5</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、记录中数组字段名存在，指定的值也存在
+2、记录中数组字段名存在，指定的值不存在
+3、记录中数组字段名不存在
+4、字段值有效取值  ---同$inc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>更新符：$pull，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
+语法：{$pull:{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;字段名1&gt;:&lt;值1&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>更新符：$pull_all，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
+语法：{$pull_all:{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>更新符：$push，将给定数值插入到目标数组中，操作对象必须为数组类型的字段。如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
+语法：{$push:{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;字段名1&gt;:&lt;值1&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
+语法：{$push_all:{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Json 对象，格式：{&lt;{""更新符1"":{"字段名1":"值"},"更新符2":{"字段名2":"值2"},...}&gt;,[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}],[{"":"索引名"|null}]}
+upsert暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，则跳过不更新。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Json 对象，格式：{""更新符1"":{字段名1:"值"},"更新符2":{"字段名2":"值2"},...}
+update暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，跳过不更新。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2512,7 +2623,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2597,6 +2708,42 @@
     <font>
       <sz val="10.5"/>
       <color theme="9" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2706,7 +2853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2753,8 +2900,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2780,23 +2930,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3095,368 +3251,368 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="27.75" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="26.125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="31.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="33" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="31" customWidth="1"/>
+    <col min="4" max="4" width="32.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="28.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="33.25" style="4" customWidth="1"/>
     <col min="8" max="8" width="26.5" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="25.5">
+      <c r="A2" s="30"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
-    <row r="3" spans="1:8" ht="127.5">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:8" ht="102">
+      <c r="A3" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>17</v>
+      <c r="C3" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>62</v>
+        <v>90</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>91</v>
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="323.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="26"/>
+    <row r="4" spans="1:8" ht="309.75">
+      <c r="A4" s="27"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>103</v>
+        <v>58</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="76.5">
-      <c r="A5" s="29"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="29"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>30</v>
+        <v>59</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="153">
-      <c r="A7" s="29"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="26"/>
+    <row r="7" spans="1:8" ht="114.75">
+      <c r="A7" s="27"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>41</v>
+        <v>61</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" ht="153">
-      <c r="A8" s="29"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="26"/>
+    <row r="8" spans="1:8" ht="140.25">
+      <c r="A8" s="27"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>35</v>
+        <v>98</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8" ht="102">
-      <c r="A9" s="29"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="26"/>
+    <row r="9" spans="1:8" ht="89.25">
+      <c r="A9" s="27"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:8" ht="127.5">
-      <c r="A10" s="29"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="26"/>
+    <row r="10" spans="1:8" ht="114.75" customHeight="1">
+      <c r="A10" s="27"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:8" ht="140.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="26"/>
+    <row r="11" spans="1:8" ht="89.25">
+      <c r="A11" s="27"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" ht="140.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="26"/>
+    <row r="12" spans="1:8" ht="114.75">
+      <c r="A12" s="27"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="127.5">
-      <c r="A13" s="29"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="27"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>49</v>
+        <v>27</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="11" t="s">
-        <v>18</v>
+    <row r="14" spans="1:8" ht="76.5">
+      <c r="A14" s="27"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="102">
-      <c r="A15" s="29"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="11" t="s">
-        <v>19</v>
+    <row r="15" spans="1:8" ht="89.25">
+      <c r="A15" s="27"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" ht="153">
-      <c r="A16" s="29"/>
-      <c r="B16" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>15</v>
+    <row r="16" spans="1:8" ht="102">
+      <c r="A16" s="27"/>
+      <c r="B16" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="102">
-      <c r="A17" s="29"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="11" t="s">
-        <v>16</v>
+      <c r="A17" s="27"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="29"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="11" t="s">
-        <v>54</v>
+      <c r="A18" s="27"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="25.5">
-      <c r="A19" s="30"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="14" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="8" t="s">
@@ -3465,198 +3621,198 @@
       <c r="F19" s="1"/>
       <c r="G19" s="11"/>
       <c r="H19" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="53.25">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:8" ht="66.75">
+      <c r="A20" s="32" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>64</v>
+        <v>36</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" ht="53.25">
-      <c r="A21" s="16"/>
+    <row r="21" spans="1:8" ht="66.75">
+      <c r="A21" s="32"/>
       <c r="B21" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>71</v>
+        <v>37</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="53.25" customHeight="1">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>71</v>
+      <c r="A22" s="32"/>
+      <c r="B22" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" ht="78.75">
-      <c r="A23" s="16"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="1" t="s">
+    <row r="23" spans="1:8" ht="91.5">
+      <c r="A23" s="32"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>85</v>
+      <c r="F23" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="38.25">
-      <c r="A24" s="16"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="13" t="s">
-        <v>74</v>
+    <row r="24" spans="1:8" ht="26.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="53.25">
-      <c r="A25" s="16"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="13" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="8"/>
       <c r="F25" s="1" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="64.5">
-      <c r="A26" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>88</v>
+      <c r="A26" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>94</v>
+        <v>68</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="63.75">
-      <c r="A27" s="16"/>
-      <c r="B27" s="18"/>
+    <row r="27" spans="1:8" ht="51">
+      <c r="A27" s="32"/>
+      <c r="B27" s="19"/>
       <c r="C27" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="53.25">
-      <c r="A28" s="16"/>
+    <row r="28" spans="1:8" ht="66.75">
+      <c r="A28" s="32"/>
       <c r="B28" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>89</v>
+        <v>55</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>101</v>
+        <v>70</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
     </row>
@@ -3681,6 +3837,7 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
+++ b/internal_doc/05.测试设计/参数校验/基本操作参数校验测试设计（update upsert lob subCL）_hxn.xlsx
@@ -2906,11 +2906,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2918,13 +2918,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2939,20 +2945,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3251,9 +3251,9 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="33" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="19" customWidth="1"/>
     <col min="2" max="2" width="16.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="31" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="18" customWidth="1"/>
     <col min="4" max="4" width="32.75" style="4" customWidth="1"/>
     <col min="5" max="5" width="4.375" style="9" customWidth="1"/>
     <col min="6" max="6" width="28.25" style="4" customWidth="1"/>
@@ -3263,19 +3263,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="23"/>
+      <c r="E1" s="32"/>
       <c r="F1" s="20" t="s">
         <v>6</v>
       </c>
@@ -3287,9 +3287,9 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" ht="25.5">
-      <c r="A2" s="30"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="21"/>
-      <c r="C2" s="30"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
@@ -3301,13 +3301,13 @@
       <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="102">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="25" t="s">
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -3325,9 +3325,9 @@
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="309.75">
-      <c r="A4" s="27"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="1" t="s">
         <v>93</v>
       </c>
@@ -3343,9 +3343,9 @@
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="76.5">
-      <c r="A5" s="27"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="1" t="s">
         <v>94</v>
       </c>
@@ -3361,9 +3361,9 @@
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="27"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="1" t="s">
         <v>95</v>
       </c>
@@ -3379,9 +3379,9 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" ht="114.75">
-      <c r="A7" s="27"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="1" t="s">
         <v>96</v>
       </c>
@@ -3397,9 +3397,9 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" ht="140.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="1" t="s">
         <v>97</v>
       </c>
@@ -3415,9 +3415,9 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" ht="89.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="1" t="s">
         <v>100</v>
       </c>
@@ -3433,9 +3433,9 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="114.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="1" t="s">
         <v>101</v>
       </c>
@@ -3451,9 +3451,9 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" ht="89.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="1" t="s">
         <v>102</v>
       </c>
@@ -3469,9 +3469,9 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" ht="114.75">
-      <c r="A12" s="27"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="1" t="s">
         <v>103</v>
       </c>
@@ -3487,9 +3487,9 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="127.5">
-      <c r="A13" s="27"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="1" t="s">
         <v>75</v>
       </c>
@@ -3505,8 +3505,8 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="76.5">
-      <c r="A14" s="27"/>
-      <c r="B14" s="24"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="16" t="s">
         <v>16</v>
       </c>
@@ -3527,8 +3527,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="89.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="24"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="16" t="s">
         <v>17</v>
       </c>
@@ -3547,8 +3547,8 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" ht="102">
-      <c r="A16" s="27"/>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="25" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="16" t="s">
@@ -3569,8 +3569,8 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="102">
-      <c r="A17" s="27"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="16" t="s">
         <v>15</v>
       </c>
@@ -3589,8 +3589,8 @@
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="27"/>
-      <c r="B18" s="19"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="16" t="s">
         <v>30</v>
       </c>
@@ -3609,8 +3609,8 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="25.5">
-      <c r="A19" s="28"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="14" t="s">
         <v>31</v>
       </c>
@@ -3625,7 +3625,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="66.75">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="24" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="12" t="s">
@@ -3649,7 +3649,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="66.75">
-      <c r="A21" s="32"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="13" t="s">
         <v>37</v>
       </c>
@@ -3671,8 +3671,8 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="53.25" customHeight="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="18" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="16" t="s">
@@ -3693,8 +3693,8 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="91.5">
-      <c r="A23" s="32"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="16" t="s">
         <v>85</v>
       </c>
@@ -3713,8 +3713,8 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="26.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="25"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="27"/>
       <c r="C24" s="17" t="s">
         <v>67</v>
       </c>
@@ -3733,7 +3733,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="53.25">
-      <c r="A25" s="32"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="13" t="s">
         <v>46</v>
       </c>
@@ -3751,10 +3751,10 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="64.5">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="25" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -3775,8 +3775,8 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="51">
-      <c r="A27" s="32"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="1" t="s">
         <v>88</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="66.75">
-      <c r="A28" s="32"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="13" t="s">
         <v>55</v>
       </c>
@@ -3818,6 +3818,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -3826,13 +3833,6 @@
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A3:A19"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="B22:B24"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
